--- a/src/mars/analysis/mars_bin_report_linux.xlsx
+++ b/src/mars/analysis/mars_bin_report_linux.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
-  <workbookPr defaultThemeVersion="124226"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <workbookPr hidePivotFieldList="1" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\mars-risk\src\mars\analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E65C162-D721-4A8E-8983-6CD49DBE81FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87CF90C6-A148-4043-B657-2517872A916C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="24196" windowHeight="14476" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="24196" windowHeight="14476" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="分组透视" sheetId="4" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="55">
   <si>
     <t>y</t>
   </si>
@@ -207,15 +207,19 @@
     <t>trend</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>iv</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="176" formatCode="#,##0.000;[Red]\-#,##0.000"/>
     <numFmt numFmtId="177" formatCode="#,##0_ ;[Red]\-#,##0\ "/>
     <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
+    <numFmt numFmtId="179" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -296,7 +300,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" pivotButton="1" applyFont="1"/>
@@ -344,11 +348,1153 @@
     </xf>
     <xf numFmtId="10" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="178" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="179" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="302">
+  <dxfs count="376">
+    <dxf>
+      <numFmt numFmtId="179" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <sz val="9"/>
+        <color theme="1" tint="4.9989318521683403E-2"/>
+      </font>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1" tint="4.9989318521683403E-2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="9"/>
+      </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1" tint="4.9989318521683403E-2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="9"/>
+      </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+        <charset val="134"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+        <charset val="134"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+        <charset val="134"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+        <charset val="134"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+        <charset val="134"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+        <charset val="134"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+        <charset val="134"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+        <charset val="134"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+        <charset val="134"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+        <charset val="134"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1" tint="4.9989318521683403E-2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="9"/>
+      </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
+    </dxf>
     <dxf>
       <font>
         <color theme="0"/>
@@ -410,64 +1556,7 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <sz val="8"/>
-        <charset val="134"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-        <charset val="134"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-        <charset val="134"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-        <charset val="134"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-        <charset val="134"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-        <charset val="134"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-        <charset val="134"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-        <charset val="134"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-        <charset val="134"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-        <charset val="134"/>
-      </font>
+      <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
     </dxf>
     <dxf>
       <font>
@@ -550,126 +1639,186 @@
       </font>
     </dxf>
     <dxf>
+      <font>
+        <sz val="8"/>
+        <charset val="134"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+        <charset val="134"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+        <charset val="134"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+        <charset val="134"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+        <charset val="134"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+        <charset val="134"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+        <charset val="134"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+        <charset val="134"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+        <charset val="134"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+        <charset val="134"/>
+      </font>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
     </dxf>
     <dxf>
       <font>
-        <name val="微软雅黑"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
       </font>
     </dxf>
     <dxf>
@@ -677,98 +1826,98 @@
     </dxf>
     <dxf>
       <font>
-        <name val="微软雅黑"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
       </font>
     </dxf>
     <dxf>
@@ -776,393 +1925,259 @@
     </dxf>
     <dxf>
       <font>
-        <name val="微软雅黑"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
       </font>
     </dxf>
     <dxf>
       <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
     </dxf>
     <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-      </font>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
     </dxf>
     <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
     </dxf>
     <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-      </font>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="9"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1" tint="4.9989318521683403E-2"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -1171,23 +2186,154 @@
       </font>
     </dxf>
     <dxf>
-      <font>
-        <color theme="1" tint="4.9989318521683403E-2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="9"/>
-      </font>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -1489,786 +2635,6 @@
         <name val="微软雅黑"/>
         <family val="2"/>
         <charset val="134"/>
-      </font>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-        <charset val="134"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-        <charset val="134"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-        <charset val="134"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-        <charset val="134"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-        <charset val="134"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-        <charset val="134"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-        <charset val="134"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-        <charset val="134"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-        <charset val="134"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-        <charset val="134"/>
-      </font>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="9"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1" tint="4.9989318521683403E-2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="8"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <charset val="134"/>
-        <scheme val="none"/>
       </font>
     </dxf>
   </dxfs>
@@ -2285,11 +2651,11 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="李士强" refreshedDate="46062.019429282409" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="2" xr:uid="{52F49DAE-8B10-4720-B763-EACA38E5035D}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="李士强" refreshedDate="46112.366218634263" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="2" xr:uid="{52F49DAE-8B10-4720-B763-EACA38E5035D}">
   <cacheSource type="worksheet">
     <worksheetSource name="detail"/>
   </cacheSource>
-  <cacheFields count="20">
+  <cacheFields count="21">
     <cacheField name="y" numFmtId="0">
       <sharedItems containsNonDate="0" containsBlank="1" count="3">
         <m/>
@@ -2322,6 +2688,9 @@
         <s v="feat_stable_04" u="1"/>
         <s v="none" u="1"/>
       </sharedItems>
+    </cacheField>
+    <cacheField name="trend" numFmtId="0">
+      <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
     </cacheField>
     <cacheField name="mars_group" numFmtId="0">
       <sharedItems count="1">
@@ -2515,6 +2884,7 @@
   <r>
     <x v="0"/>
     <x v="0"/>
+    <m/>
     <x v="0"/>
     <n v="-1"/>
     <x v="0"/>
@@ -2537,6 +2907,7 @@
   <r>
     <x v="0"/>
     <x v="0"/>
+    <m/>
     <x v="0"/>
     <n v="-1"/>
     <x v="1"/>
@@ -2561,8 +2932,8 @@
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1E6BA4EB-C9E7-419D-885D-D579A93B5FA1}" name="分组透视" cacheId="8" dataPosition="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Feature" colHeaderCaption="Group">
-  <location ref="A5:F10" firstHeaderRow="1" firstDataRow="3" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
-  <pivotFields count="20">
+  <location ref="A5:G10" firstHeaderRow="1" firstDataRow="3" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
+  <pivotFields count="21">
     <pivotField axis="axisPage" showAll="0">
       <items count="4">
         <item m="1" x="2"/>
@@ -2597,6 +2968,7 @@
         <item x="0"/>
       </items>
     </pivotField>
+    <pivotField showAll="0"/>
     <pivotField axis="axisCol" showAll="0">
       <items count="2">
         <item x="0"/>
@@ -2738,7 +3110,7 @@
     <pivotField numFmtId="176" showAll="0"/>
     <pivotField numFmtId="176" showAll="0"/>
     <pivotField numFmtId="176" showAll="0"/>
-    <pivotField numFmtId="176" showAll="0"/>
+    <pivotField dataField="1" numFmtId="176" showAll="0"/>
     <pivotField numFmtId="177" showAll="0"/>
     <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
       <items count="4">
@@ -2751,7 +3123,7 @@
   </pivotFields>
   <rowFields count="2">
     <field x="1"/>
-    <field x="4"/>
+    <field x="5"/>
   </rowFields>
   <rowItems count="3">
     <i>
@@ -2766,9 +3138,9 @@
   </rowItems>
   <colFields count="2">
     <field x="-2"/>
-    <field x="2"/>
+    <field x="3"/>
   </colFields>
-  <colItems count="5">
+  <colItems count="6">
     <i>
       <x/>
       <x/>
@@ -2789,56 +3161,61 @@
       <x v="4"/>
       <x/>
     </i>
+    <i i="5">
+      <x v="5"/>
+      <x/>
+    </i>
   </colItems>
   <pageFields count="2">
     <pageField fld="0" hier="-1"/>
-    <pageField fld="19" hier="-1"/>
+    <pageField fld="20" hier="-1"/>
   </pageFields>
-  <dataFields count="5">
-    <dataField name="pct " fld="8" baseField="4" baseItem="115" numFmtId="176"/>
-    <dataField name="risk" fld="9" baseField="1" baseItem="21" numFmtId="176"/>
-    <dataField name="lift " fld="10" baseField="1" baseItem="21" numFmtId="176"/>
-    <dataField name="bad count" fld="6" baseField="1" baseItem="21" numFmtId="38"/>
-    <dataField name="total count" fld="5" baseField="1" baseItem="21" numFmtId="38"/>
+  <dataFields count="6">
+    <dataField name="pct " fld="9" baseField="4" baseItem="115" numFmtId="176"/>
+    <dataField name="risk" fld="10" baseField="1" baseItem="21" numFmtId="176"/>
+    <dataField name="lift " fld="11" baseField="1" baseItem="21" numFmtId="176"/>
+    <dataField name="bad count" fld="7" baseField="1" baseItem="21" numFmtId="38"/>
+    <dataField name="total count" fld="6" baseField="1" baseItem="21" numFmtId="38"/>
+    <dataField name="iv" fld="18" baseField="1" baseItem="21" numFmtId="176"/>
   </dataFields>
-  <formats count="36">
-    <format dxfId="301">
+  <formats count="38">
+    <format dxfId="353">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="300">
+    <format dxfId="352">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="299">
+    <format dxfId="351">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="298">
+    <format dxfId="350">
       <pivotArea field="-2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="297">
+    <format dxfId="349">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="296">
+    <format dxfId="348">
       <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="295">
+    <format dxfId="347">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="1" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="294">
+    <format dxfId="346">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="293">
+    <format dxfId="345">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="2">
           <reference field="1" count="0" selected="0"/>
-          <reference field="4" count="0"/>
+          <reference field="5" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="292">
+    <format dxfId="344">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="5">
@@ -2851,43 +3228,43 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="291">
+    <format dxfId="343">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="290">
+    <format dxfId="342">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="289">
+    <format dxfId="341">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="288">
+    <format dxfId="340">
       <pivotArea field="-2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="287">
+    <format dxfId="339">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="286">
+    <format dxfId="338">
       <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="285">
+    <format dxfId="337">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="1" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="284">
+    <format dxfId="336">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="283">
+    <format dxfId="335">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="2">
           <reference field="1" count="0" selected="0"/>
-          <reference field="4" count="0"/>
+          <reference field="5" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="282">
+    <format dxfId="334">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="5">
@@ -2900,19 +3277,19 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="281">
+    <format dxfId="333">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="280">
+    <format dxfId="332">
       <pivotArea field="-2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="279">
+    <format dxfId="331">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="278">
+    <format dxfId="330">
       <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="277">
+    <format dxfId="329">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="5">
@@ -2925,19 +3302,19 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="276">
+    <format dxfId="328">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="275">
+    <format dxfId="327">
       <pivotArea field="-2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="274">
+    <format dxfId="326">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="273">
+    <format dxfId="325">
       <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="272">
+    <format dxfId="324">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="5">
@@ -2950,7 +3327,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="271">
+    <format dxfId="323">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="5">
@@ -2963,7 +3340,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="270">
+    <format dxfId="322">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="5">
@@ -2976,7 +3353,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="269">
+    <format dxfId="321">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="5">
@@ -2989,39 +3366,60 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="268">
+    <format dxfId="320">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="4">
           <reference field="4294967294" count="1" selected="0">
             <x v="0"/>
           </reference>
           <reference field="1" count="0" selected="0"/>
-          <reference field="2" count="0" selected="0"/>
-          <reference field="4" count="0"/>
+          <reference field="3" count="0" selected="0"/>
+          <reference field="5" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="267">
+    <format dxfId="319">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="4">
           <reference field="4294967294" count="1" selected="0">
             <x v="1"/>
           </reference>
           <reference field="1" count="0" selected="0"/>
-          <reference field="2" count="0" selected="0"/>
-          <reference field="4" count="0"/>
+          <reference field="3" count="0" selected="0"/>
+          <reference field="5" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="266">
+    <format dxfId="318">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="4">
           <reference field="4294967294" count="1" selected="0">
             <x v="2"/>
           </reference>
           <reference field="1" count="0" selected="0"/>
-          <reference field="2" count="0" selected="0"/>
-          <reference field="4" count="0"/>
+          <reference field="3" count="0" selected="0"/>
+          <reference field="5" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="1">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1">
+            <x v="5"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="0">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="4">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="5"/>
+          </reference>
+          <reference field="1" count="0" selected="0"/>
+          <reference field="3" count="0" selected="0" defaultSubtotal="1" sumSubtotal="1" countASubtotal="1" avgSubtotal="1" maxSubtotal="1" minSubtotal="1" productSubtotal="1" countSubtotal="1" stdDevSubtotal="1" stdDevPSubtotal="1" varSubtotal="1" varPSubtotal="1"/>
+          <reference field="5" count="0"/>
         </references>
       </pivotArea>
     </format>
@@ -3041,7 +3439,7 @@
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C980371C-D21C-4C39-9001-37938B72DAD7}" name="数据透视表1" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Feature">
   <location ref="A5:F6" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
-  <pivotFields count="20">
+  <pivotFields count="21">
     <pivotField axis="axisPage" showAll="0">
       <items count="4">
         <item m="1" x="2"/>
@@ -3077,6 +3475,7 @@
         <item t="default"/>
       </items>
     </pivotField>
+    <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField numFmtId="38" showAll="0"/>
     <pivotField axis="axisPage" showAll="0">
@@ -3247,36 +3646,36 @@
   </colItems>
   <pageFields count="2">
     <pageField fld="0" hier="-1"/>
-    <pageField fld="4" item="116" hier="-1"/>
+    <pageField fld="5" item="116" hier="-1"/>
   </pageFields>
   <dataFields count="5">
-    <dataField name="max(PSI) " fld="14" subtotal="max" baseField="1" baseItem="21" numFmtId="178"/>
-    <dataField name="avg(IV) " fld="17" subtotal="average" baseField="1" baseItem="21" numFmtId="178"/>
-    <dataField name="avg(KS) " fld="15" subtotal="average" baseField="1" baseItem="21" numFmtId="178"/>
-    <dataField name="max(Lift) " fld="10" subtotal="max" baseField="1" baseItem="21" numFmtId="178"/>
-    <dataField name="avg(AUC) " fld="16" subtotal="average" baseField="1" baseItem="21" numFmtId="178"/>
+    <dataField name="max(PSI) " fld="15" subtotal="max" baseField="1" baseItem="21" numFmtId="178"/>
+    <dataField name="avg(IV) " fld="18" subtotal="average" baseField="1" baseItem="21" numFmtId="178"/>
+    <dataField name="avg(KS) " fld="16" subtotal="average" baseField="1" baseItem="21" numFmtId="178"/>
+    <dataField name="max(Lift) " fld="11" subtotal="max" baseField="1" baseItem="21" numFmtId="178"/>
+    <dataField name="avg(AUC) " fld="17" subtotal="average" baseField="1" baseItem="21" numFmtId="178"/>
   </dataFields>
   <formats count="15">
-    <format dxfId="265">
+    <format dxfId="317">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="264">
+    <format dxfId="316">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="263">
+    <format dxfId="315">
       <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="262">
+    <format dxfId="314">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="1" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="261">
+    <format dxfId="313">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="260">
+    <format dxfId="312">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="5">
@@ -3289,26 +3688,26 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="259">
+    <format dxfId="311">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="258">
+    <format dxfId="310">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="257">
+    <format dxfId="309">
       <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="256">
+    <format dxfId="308">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="1" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="255">
+    <format dxfId="307">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="254">
+    <format dxfId="306">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="5">
@@ -3321,7 +3720,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="253">
+    <format dxfId="305">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -3330,7 +3729,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="252">
+    <format dxfId="304">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="4" selected="0">
@@ -3342,7 +3741,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="251">
+    <format dxfId="303">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -3367,7 +3766,7 @@
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9AD699F8-3343-40F3-BC8D-6736B2D98F6C}" name="Missing" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Feature" colHeaderCaption="Group">
   <location ref="A4:B6" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
-  <pivotFields count="20">
+  <pivotFields count="21">
     <pivotField axis="axisPage" showAll="0">
       <items count="4">
         <item m="1" x="1"/>
@@ -3403,6 +3802,7 @@
         <item t="default"/>
       </items>
     </pivotField>
+    <pivotField showAll="0"/>
     <pivotField axis="axisCol" showAll="0">
       <items count="2">
         <item x="0"/>
@@ -3557,7 +3957,7 @@
     </i>
   </rowItems>
   <colFields count="1">
-    <field x="2"/>
+    <field x="3"/>
   </colFields>
   <colItems count="1">
     <i>
@@ -3566,44 +3966,44 @@
   </colItems>
   <pageFields count="2">
     <pageField fld="0" hier="-1"/>
-    <pageField fld="4" item="115" hier="-1"/>
+    <pageField fld="5" item="115" hier="-1"/>
   </pageFields>
   <dataFields count="1">
-    <dataField name="Missing rate" fld="8" baseField="1" baseItem="3" numFmtId="10"/>
+    <dataField name="Missing rate" fld="9" baseField="1" baseItem="3" numFmtId="10"/>
   </dataFields>
   <formats count="10">
-    <format dxfId="250">
+    <format dxfId="302">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="249">
+    <format dxfId="301">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="248">
+    <format dxfId="300">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="247">
+    <format dxfId="299">
       <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="246">
+    <format dxfId="298">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="1" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="245">
+    <format dxfId="297">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="244">
+    <format dxfId="296">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="243">
+    <format dxfId="295">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="242">
+    <format dxfId="294">
       <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="241">
+    <format dxfId="293">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="1" count="0"/>
@@ -3626,7 +4026,7 @@
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{67F0994E-2D0E-416D-B233-2A068F2B0705}" name="PSI" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Feature" colHeaderCaption="Group">
   <location ref="A4:B6" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
-  <pivotFields count="20">
+  <pivotFields count="21">
     <pivotField axis="axisPage" showAll="0">
       <items count="4">
         <item m="1" x="2"/>
@@ -3662,6 +4062,7 @@
         <item t="default"/>
       </items>
     </pivotField>
+    <pivotField showAll="0"/>
     <pivotField axis="axisCol" showAll="0">
       <items count="2">
         <item x="0"/>
@@ -3816,7 +4217,7 @@
     </i>
   </rowItems>
   <colFields count="1">
-    <field x="2"/>
+    <field x="3"/>
   </colFields>
   <colItems count="1">
     <i>
@@ -3825,69 +4226,69 @@
   </colItems>
   <pageFields count="2">
     <pageField fld="0" hier="-1"/>
-    <pageField fld="4" item="116" hier="-1"/>
+    <pageField fld="5" item="116" hier="-1"/>
   </pageFields>
   <dataFields count="1">
-    <dataField name="PSI" fld="14" subtotal="max" baseField="1" baseItem="21" numFmtId="178"/>
+    <dataField name="PSI" fld="15" subtotal="max" baseField="1" baseItem="21" numFmtId="178"/>
   </dataFields>
   <formats count="17">
-    <format dxfId="240">
+    <format dxfId="292">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="239">
+    <format dxfId="291">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="238">
+    <format dxfId="290">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="237">
+    <format dxfId="289">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="236">
+    <format dxfId="288">
       <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="235">
+    <format dxfId="287">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="1" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="234">
+    <format dxfId="286">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="233">
+    <format dxfId="285">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="232">
+    <format dxfId="284">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="231">
+    <format dxfId="283">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="230">
+    <format dxfId="282">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="229">
+    <format dxfId="281">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="228">
+    <format dxfId="280">
       <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="227">
+    <format dxfId="279">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="1" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="226">
+    <format dxfId="278">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="225">
+    <format dxfId="277">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="224">
+    <format dxfId="276">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -3906,7 +4307,7 @@
 <file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{140390A3-C4DA-44CD-8D5D-1808099448B4}" name="IV" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Feature" colHeaderCaption="Group">
   <location ref="A4:B6" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
-  <pivotFields count="20">
+  <pivotFields count="21">
     <pivotField axis="axisPage" showAll="0">
       <items count="4">
         <item m="1" x="2"/>
@@ -3942,6 +4343,7 @@
         <item t="default"/>
       </items>
     </pivotField>
+    <pivotField showAll="0"/>
     <pivotField axis="axisCol" showAll="0">
       <items count="2">
         <item x="0"/>
@@ -4096,7 +4498,7 @@
     </i>
   </rowItems>
   <colFields count="1">
-    <field x="2"/>
+    <field x="3"/>
   </colFields>
   <colItems count="1">
     <i>
@@ -4105,69 +4507,69 @@
   </colItems>
   <pageFields count="2">
     <pageField fld="0" hier="-1"/>
-    <pageField fld="4" item="116" hier="-1"/>
+    <pageField fld="5" item="116" hier="-1"/>
   </pageFields>
   <dataFields count="1">
-    <dataField name="IV" fld="17" baseField="1" baseItem="21" numFmtId="178"/>
+    <dataField name="IV" fld="18" baseField="1" baseItem="21" numFmtId="178"/>
   </dataFields>
   <formats count="17">
-    <format dxfId="223">
+    <format dxfId="275">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="222">
+    <format dxfId="274">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="221">
+    <format dxfId="273">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="220">
+    <format dxfId="272">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="219">
+    <format dxfId="271">
       <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="218">
+    <format dxfId="270">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="1" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="217">
+    <format dxfId="269">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="216">
+    <format dxfId="268">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="215">
+    <format dxfId="267">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="214">
+    <format dxfId="266">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="213">
+    <format dxfId="265">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="212">
+    <format dxfId="264">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="211">
+    <format dxfId="263">
       <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="210">
+    <format dxfId="262">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="1" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="209">
+    <format dxfId="261">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="208">
+    <format dxfId="260">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="207">
+    <format dxfId="259">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -4186,7 +4588,7 @@
 <file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7B34FFD6-1423-4AE2-85E9-3157863EBEBF}" name="数据透视表2" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Feature" colHeaderCaption="Group">
   <location ref="A4:B6" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
-  <pivotFields count="20">
+  <pivotFields count="21">
     <pivotField axis="axisPage" showAll="0">
       <items count="4">
         <item m="1" x="2"/>
@@ -4222,6 +4624,7 @@
         <item t="default"/>
       </items>
     </pivotField>
+    <pivotField showAll="0"/>
     <pivotField axis="axisCol" showAll="0">
       <items count="2">
         <item x="0"/>
@@ -4376,7 +4779,7 @@
     </i>
   </rowItems>
   <colFields count="1">
-    <field x="2"/>
+    <field x="3"/>
   </colFields>
   <colItems count="1">
     <i>
@@ -4385,89 +4788,89 @@
   </colItems>
   <pageFields count="2">
     <pageField fld="0" hier="-1"/>
-    <pageField fld="4" item="116" hier="-1"/>
+    <pageField fld="5" item="116" hier="-1"/>
   </pageFields>
   <dataFields count="1">
-    <dataField name="KS" fld="15" subtotal="max" baseField="2" baseItem="0" numFmtId="178"/>
+    <dataField name="KS" fld="16" subtotal="max" baseField="2" baseItem="0" numFmtId="178"/>
   </dataFields>
   <formats count="21">
-    <format dxfId="206">
+    <format dxfId="258">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="205">
+    <format dxfId="257">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="204">
+    <format dxfId="256">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="203">
-      <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
-    </format>
-    <format dxfId="202">
+    <format dxfId="255">
+      <pivotArea field="3" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
+    </format>
+    <format dxfId="254">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="201">
+    <format dxfId="253">
       <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="200">
+    <format dxfId="252">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="1" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="199">
+    <format dxfId="251">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="198">
+    <format dxfId="250">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
-          <reference field="2" count="0"/>
+          <reference field="3" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="197">
+    <format dxfId="249">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="196">
+    <format dxfId="248">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="195">
+    <format dxfId="247">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="194">
+    <format dxfId="246">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="193">
-      <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
-    </format>
-    <format dxfId="192">
+    <format dxfId="245">
+      <pivotArea field="3" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
+    </format>
+    <format dxfId="244">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="191">
+    <format dxfId="243">
       <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="190">
+    <format dxfId="242">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="1" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="189">
+    <format dxfId="241">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="188">
+    <format dxfId="240">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
-          <reference field="2" count="0"/>
+          <reference field="3" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="187">
+    <format dxfId="239">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="186">
+    <format dxfId="238">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -4486,7 +4889,7 @@
 <file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E1C2EDF3-DA9D-4B5F-A88A-9AED0257874E}" name="数据透视表3" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Feature" colHeaderCaption="Group">
   <location ref="A4:B6" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
-  <pivotFields count="20">
+  <pivotFields count="21">
     <pivotField axis="axisPage" showAll="0">
       <items count="4">
         <item m="1" x="2"/>
@@ -4522,6 +4925,7 @@
         <item t="default"/>
       </items>
     </pivotField>
+    <pivotField showAll="0"/>
     <pivotField axis="axisCol" showAll="0">
       <items count="2">
         <item x="0"/>
@@ -4676,7 +5080,7 @@
     </i>
   </rowItems>
   <colFields count="1">
-    <field x="2"/>
+    <field x="3"/>
   </colFields>
   <colItems count="1">
     <i>
@@ -4685,89 +5089,89 @@
   </colItems>
   <pageFields count="2">
     <pageField fld="0" hier="-1"/>
-    <pageField fld="4" item="116" hier="-1"/>
+    <pageField fld="5" item="116" hier="-1"/>
   </pageFields>
   <dataFields count="1">
-    <dataField name="AUC" fld="16" subtotal="max" baseField="1" baseItem="21" numFmtId="178"/>
+    <dataField name="AUC" fld="17" subtotal="max" baseField="1" baseItem="21" numFmtId="178"/>
   </dataFields>
   <formats count="21">
-    <format dxfId="185">
+    <format dxfId="237">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="184">
+    <format dxfId="236">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="183">
+    <format dxfId="235">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="182">
-      <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
-    </format>
-    <format dxfId="181">
+    <format dxfId="234">
+      <pivotArea field="3" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
+    </format>
+    <format dxfId="233">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="180">
+    <format dxfId="232">
       <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="179">
+    <format dxfId="231">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="1" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="178">
+    <format dxfId="230">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="177">
+    <format dxfId="229">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
-          <reference field="2" count="0"/>
+          <reference field="3" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="176">
+    <format dxfId="228">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="175">
+    <format dxfId="227">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="174">
+    <format dxfId="226">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="173">
+    <format dxfId="225">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="172">
-      <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
-    </format>
-    <format dxfId="171">
+    <format dxfId="224">
+      <pivotArea field="3" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
+    </format>
+    <format dxfId="223">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="170">
+    <format dxfId="222">
       <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="169">
+    <format dxfId="221">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="1" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="168">
+    <format dxfId="220">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="167">
+    <format dxfId="219">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
-          <reference field="2" count="0"/>
+          <reference field="3" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="166">
+    <format dxfId="218">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="165">
+    <format dxfId="217">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -4784,30 +5188,30 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{73489535-5F3C-4236-A955-4E0C5ACDF166}" name="detail" displayName="detail" ref="A1:U3" totalsRowShown="0" headerRowDxfId="164" dataDxfId="163">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{73489535-5F3C-4236-A955-4E0C5ACDF166}" name="detail" displayName="detail" ref="A1:U3" totalsRowShown="0" headerRowDxfId="375" dataDxfId="374">
   <autoFilter ref="A1:U3" xr:uid="{73489535-5F3C-4236-A955-4E0C5ACDF166}"/>
   <tableColumns count="21">
-    <tableColumn id="1" xr3:uid="{847E9846-5D09-4B22-96D7-00A15E265DF1}" name="y" dataDxfId="162"/>
-    <tableColumn id="2" xr3:uid="{A302BC46-C3F8-480A-BCEE-CC2B73F6B6AD}" name="feature" dataDxfId="161"/>
+    <tableColumn id="1" xr3:uid="{847E9846-5D09-4B22-96D7-00A15E265DF1}" name="y" dataDxfId="373"/>
+    <tableColumn id="2" xr3:uid="{A302BC46-C3F8-480A-BCEE-CC2B73F6B6AD}" name="feature" dataDxfId="372"/>
     <tableColumn id="20" xr3:uid="{C31E309C-2FD8-4148-B022-9A791C9E581F}" name="trend"/>
-    <tableColumn id="3" xr3:uid="{15F7C32B-EFFD-41FD-9B31-0FD89CCE1558}" name="mars_group" dataDxfId="160"/>
-    <tableColumn id="4" xr3:uid="{E0412AC0-75F8-47FC-9AFE-DCC4E408E83E}" name="bin_index" dataDxfId="159"/>
-    <tableColumn id="5" xr3:uid="{441B9B96-D32B-4467-BF91-7B8716B0EE73}" name="bin_label" dataDxfId="158"/>
-    <tableColumn id="6" xr3:uid="{7727AFD4-5E39-4798-91A2-841BCB625955}" name="count" dataDxfId="157"/>
-    <tableColumn id="7" xr3:uid="{6904BB63-FC08-4541-9B35-574D79859015}" name="bad" dataDxfId="156"/>
-    <tableColumn id="8" xr3:uid="{A2225E50-387E-446F-9407-B02F0A068262}" name="good" dataDxfId="155"/>
-    <tableColumn id="9" xr3:uid="{350FB9ED-586A-45CB-B3FA-3EECA4545E6F}" name="pct" dataDxfId="154"/>
-    <tableColumn id="10" xr3:uid="{92B3D771-6574-4A45-94E0-F3C28B2BB623}" name="bad_rate" dataDxfId="153"/>
-    <tableColumn id="11" xr3:uid="{0C7A8AE2-4171-40BA-96E5-E18FDDF74290}" name="lift" dataDxfId="152"/>
-    <tableColumn id="12" xr3:uid="{1DB142B5-C1ED-4CEA-BB78-DE1102B6241D}" name="cum_count" dataDxfId="151"/>
-    <tableColumn id="13" xr3:uid="{B7DCD3B6-CA70-4792-909A-DE823943AC34}" name="cum_bad" dataDxfId="150"/>
-    <tableColumn id="14" xr3:uid="{40C7C533-5EAC-4962-87CA-7658DA8C70CB}" name="cum_bad_rate" dataDxfId="149"/>
-    <tableColumn id="15" xr3:uid="{503E378E-7A3D-49D1-A134-2AB9BD4CABEC}" name="psi_bin" dataDxfId="148"/>
-    <tableColumn id="16" xr3:uid="{C6917BCE-A605-4BC0-8F8E-7C3EF22C93C7}" name="ks_bin" dataDxfId="147"/>
-    <tableColumn id="17" xr3:uid="{C37BE33F-0EDB-4EF8-92F6-B944648DE9A6}" name="auc_bin" dataDxfId="146"/>
-    <tableColumn id="18" xr3:uid="{68101AA9-F736-4824-80B4-F4EDB79EA91D}" name="iv_bin" dataDxfId="145"/>
-    <tableColumn id="19" xr3:uid="{0C9E5D86-5C90-4CCE-8D7B-58AB94F13C86}" name="total_count" dataDxfId="144"/>
-    <tableColumn id="21" xr3:uid="{45ABDF0B-7ED1-47FC-8BED-16F072F6736F}" name="bin_type" dataDxfId="143"/>
+    <tableColumn id="3" xr3:uid="{15F7C32B-EFFD-41FD-9B31-0FD89CCE1558}" name="mars_group" dataDxfId="371"/>
+    <tableColumn id="4" xr3:uid="{E0412AC0-75F8-47FC-9AFE-DCC4E408E83E}" name="bin_index" dataDxfId="370"/>
+    <tableColumn id="5" xr3:uid="{441B9B96-D32B-4467-BF91-7B8716B0EE73}" name="bin_label" dataDxfId="369"/>
+    <tableColumn id="6" xr3:uid="{7727AFD4-5E39-4798-91A2-841BCB625955}" name="count" dataDxfId="368"/>
+    <tableColumn id="7" xr3:uid="{6904BB63-FC08-4541-9B35-574D79859015}" name="bad" dataDxfId="367"/>
+    <tableColumn id="8" xr3:uid="{A2225E50-387E-446F-9407-B02F0A068262}" name="good" dataDxfId="366"/>
+    <tableColumn id="9" xr3:uid="{350FB9ED-586A-45CB-B3FA-3EECA4545E6F}" name="pct" dataDxfId="365"/>
+    <tableColumn id="10" xr3:uid="{92B3D771-6574-4A45-94E0-F3C28B2BB623}" name="bad_rate" dataDxfId="364"/>
+    <tableColumn id="11" xr3:uid="{0C7A8AE2-4171-40BA-96E5-E18FDDF74290}" name="lift" dataDxfId="363"/>
+    <tableColumn id="12" xr3:uid="{1DB142B5-C1ED-4CEA-BB78-DE1102B6241D}" name="cum_count" dataDxfId="362"/>
+    <tableColumn id="13" xr3:uid="{B7DCD3B6-CA70-4792-909A-DE823943AC34}" name="cum_bad" dataDxfId="361"/>
+    <tableColumn id="14" xr3:uid="{40C7C533-5EAC-4962-87CA-7658DA8C70CB}" name="cum_bad_rate" dataDxfId="360"/>
+    <tableColumn id="15" xr3:uid="{503E378E-7A3D-49D1-A134-2AB9BD4CABEC}" name="psi_bin" dataDxfId="359"/>
+    <tableColumn id="16" xr3:uid="{C6917BCE-A605-4BC0-8F8E-7C3EF22C93C7}" name="ks_bin" dataDxfId="358"/>
+    <tableColumn id="17" xr3:uid="{C37BE33F-0EDB-4EF8-92F6-B944648DE9A6}" name="auc_bin" dataDxfId="357"/>
+    <tableColumn id="18" xr3:uid="{68101AA9-F736-4824-80B4-F4EDB79EA91D}" name="iv_bin" dataDxfId="356"/>
+    <tableColumn id="19" xr3:uid="{0C9E5D86-5C90-4CCE-8D7B-58AB94F13C86}" name="total_count" dataDxfId="355"/>
+    <tableColumn id="21" xr3:uid="{45ABDF0B-7ED1-47FC-8BED-16F072F6736F}" name="bin_type" dataDxfId="354"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium6" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5109,7 +5513,7 @@
     <col min="4" max="4" width="7.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.265625" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="4.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="21.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="16.796875" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="15.6640625" style="1" bestFit="1" customWidth="1"/>
@@ -5163,7 +5567,7 @@
       <c r="D5" s="25"/>
       <c r="E5" s="25"/>
       <c r="F5" s="25"/>
-      <c r="G5"/>
+      <c r="G5" s="25"/>
       <c r="H5"/>
       <c r="I5"/>
       <c r="J5"/>
@@ -5186,7 +5590,9 @@
       <c r="F6" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="G6"/>
+      <c r="G6" s="16" t="s">
+        <v>54</v>
+      </c>
       <c r="H6"/>
       <c r="I6"/>
       <c r="J6"/>
@@ -5211,7 +5617,9 @@
       <c r="F7" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="G7"/>
+      <c r="G7" s="1" t="s">
+        <v>18</v>
+      </c>
       <c r="H7"/>
       <c r="I7"/>
       <c r="J7"/>
@@ -5226,7 +5634,7 @@
       <c r="D8" s="22"/>
       <c r="E8" s="23"/>
       <c r="F8" s="23"/>
-      <c r="G8"/>
+      <c r="G8" s="22"/>
       <c r="H8"/>
       <c r="I8"/>
       <c r="J8"/>
@@ -5251,7 +5659,9 @@
       <c r="F9" s="23">
         <v>0</v>
       </c>
-      <c r="G9"/>
+      <c r="G9" s="29">
+        <v>0</v>
+      </c>
       <c r="H9"/>
       <c r="I9"/>
       <c r="J9"/>
@@ -5276,7 +5686,9 @@
       <c r="F10" s="23">
         <v>0</v>
       </c>
-      <c r="G10"/>
+      <c r="G10" s="29">
+        <v>0</v>
+      </c>
       <c r="H10" s="14"/>
       <c r="I10"/>
       <c r="J10"/>
@@ -5530,7 +5942,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D2">
-    <cfRule type="cellIs" dxfId="5" priority="22" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="216" priority="22" operator="greaterThan">
       <formula>0.2</formula>
     </cfRule>
     <cfRule type="colorScale" priority="23">
@@ -5545,7 +5957,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2">
-    <cfRule type="cellIs" dxfId="4" priority="20" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="215" priority="20" operator="greaterThan">
       <formula>20</formula>
     </cfRule>
     <cfRule type="colorScale" priority="21">
@@ -5572,7 +5984,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2">
-    <cfRule type="cellIs" dxfId="3" priority="18" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="214" priority="18" operator="greaterThan">
       <formula>0.625</formula>
     </cfRule>
     <cfRule type="colorScale" priority="19">
@@ -5946,7 +6358,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C2">
-    <cfRule type="cellIs" dxfId="2" priority="5" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="213" priority="5" operator="greaterThan">
       <formula>0.2</formula>
     </cfRule>
     <cfRule type="colorScale" priority="6">
@@ -6030,7 +6442,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C2">
-    <cfRule type="cellIs" dxfId="1" priority="5" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="212" priority="5" operator="greaterThan">
       <formula>20</formula>
     </cfRule>
     <cfRule type="colorScale" priority="6">
@@ -6113,7 +6525,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C2">
-    <cfRule type="cellIs" dxfId="0" priority="5" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="211" priority="5" operator="greaterThan">
       <formula>0.625</formula>
     </cfRule>
     <cfRule type="colorScale" priority="6">
